--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120497320</v>
+        <v>120496283</v>
       </c>
       <c r="B6" t="n">
         <v>74654</v>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375377</v>
+        <v>375501</v>
       </c>
       <c r="R6" t="n">
-        <v>6931941</v>
+        <v>6932016</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120496283</v>
+        <v>120497872</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
+        <v>79652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1197,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375501</v>
+        <v>375194</v>
       </c>
       <c r="R7" t="n">
-        <v>6932016</v>
+        <v>6931842</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120497872</v>
+        <v>120497320</v>
       </c>
       <c r="B8" t="n">
-        <v>79652</v>
+        <v>74654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375194</v>
+        <v>375377</v>
       </c>
       <c r="R8" t="n">
-        <v>6931842</v>
+        <v>6931941</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120500426</v>
+        <v>120497639</v>
       </c>
       <c r="B12" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,41 +1707,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375202</v>
+        <v>375295</v>
       </c>
       <c r="R12" t="n">
-        <v>6931882</v>
+        <v>6931844</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120497639</v>
+        <v>120500426</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>91277</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,46 +1814,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375295</v>
+        <v>375202</v>
       </c>
       <c r="R13" t="n">
-        <v>6931844</v>
+        <v>6931882</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120496889</v>
+        <v>120496200</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,20 +1916,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1938,24 +1938,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375442</v>
+        <v>375489</v>
       </c>
       <c r="R14" t="n">
-        <v>6931967</v>
+        <v>6932031</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1999,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120496200</v>
+        <v>120496889</v>
       </c>
       <c r="B15" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,20 +2018,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2045,19 +2040,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375489</v>
+        <v>375442</v>
       </c>
       <c r="R15" t="n">
-        <v>6932031</v>
+        <v>6931967</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,12 +2101,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120496270</v>
+        <v>120501460</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,39 +2333,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375458</v>
+        <v>375193</v>
       </c>
       <c r="R18" t="n">
-        <v>6932005</v>
+        <v>6932050</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2424,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120497233</v>
+        <v>120501521</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>91277</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,13 +2459,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375377</v>
+        <v>375185</v>
       </c>
       <c r="R19" t="n">
-        <v>6931941</v>
+        <v>6932076</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2514,22 +2509,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120497371</v>
+        <v>120501264</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375373</v>
+        <v>375284</v>
       </c>
       <c r="R20" t="n">
-        <v>6931911</v>
+        <v>6932030</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120497894</v>
+        <v>120497233</v>
       </c>
       <c r="B21" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,37 +2639,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375209</v>
+        <v>375377</v>
       </c>
       <c r="R21" t="n">
-        <v>6931861</v>
+        <v>6931941</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2718,19 +2713,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120497689</v>
+        <v>120497894</v>
       </c>
       <c r="B22" t="n">
         <v>74654</v>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375261</v>
+        <v>375209</v>
       </c>
       <c r="R22" t="n">
-        <v>6931837</v>
+        <v>6931861</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120499317</v>
+        <v>120497371</v>
       </c>
       <c r="B23" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,34 +2843,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375056</v>
+        <v>375373</v>
       </c>
       <c r="R23" t="n">
-        <v>6931933</v>
+        <v>6931911</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120499806</v>
+        <v>120497689</v>
       </c>
       <c r="B24" t="n">
         <v>74654</v>
@@ -2970,14 +2965,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375096</v>
+        <v>375261</v>
       </c>
       <c r="R24" t="n">
-        <v>6932009</v>
+        <v>6931837</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120501460</v>
+        <v>120499317</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3052,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375193</v>
+        <v>375056</v>
       </c>
       <c r="R25" t="n">
-        <v>6932050</v>
+        <v>6931933</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3126,22 +3121,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120500971</v>
+        <v>120499806</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3154,34 +3149,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375284</v>
+        <v>375096</v>
       </c>
       <c r="R26" t="n">
-        <v>6931977</v>
+        <v>6932009</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120501521</v>
+        <v>120496270</v>
       </c>
       <c r="B27" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,41 +3247,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375185</v>
+        <v>375458</v>
       </c>
       <c r="R27" t="n">
-        <v>6932076</v>
+        <v>6932005</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3330,22 +3330,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120501264</v>
+        <v>120500971</v>
       </c>
       <c r="B28" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3358,21 +3358,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
         <v>375284</v>
       </c>
       <c r="R28" t="n">
-        <v>6932030</v>
+        <v>6931977</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120498167</v>
+        <v>120500133</v>
       </c>
       <c r="B29" t="n">
         <v>78542</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375259</v>
+        <v>375087</v>
       </c>
       <c r="R29" t="n">
-        <v>6931809</v>
+        <v>6931962</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120500133</v>
+        <v>120498167</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375087</v>
+        <v>375259</v>
       </c>
       <c r="R30" t="n">
-        <v>6931962</v>
+        <v>6931809</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120497004</v>
+        <v>120496215</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>74654</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,39 +3975,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>375434</v>
+        <v>375488</v>
       </c>
       <c r="R34" t="n">
-        <v>6931967</v>
+        <v>6932012</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120500798</v>
+        <v>120499540</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,21 +4077,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,13 +4101,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>375272</v>
+        <v>375059</v>
       </c>
       <c r="R35" t="n">
-        <v>6931942</v>
+        <v>6931932</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4168,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120501129</v>
+        <v>120497004</v>
       </c>
       <c r="B36" t="n">
-        <v>74654</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4184,34 +4179,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>375306</v>
+        <v>375434</v>
       </c>
       <c r="R36" t="n">
-        <v>6931998</v>
+        <v>6931967</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120496215</v>
+        <v>120500798</v>
       </c>
       <c r="B37" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,37 +4286,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>375488</v>
+        <v>375272</v>
       </c>
       <c r="R37" t="n">
-        <v>6932012</v>
+        <v>6931942</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4360,19 +4360,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120499540</v>
+        <v>120501129</v>
       </c>
       <c r="B38" t="n">
         <v>74654</v>
@@ -4408,17 +4408,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>375059</v>
+        <v>375306</v>
       </c>
       <c r="R38" t="n">
-        <v>6931932</v>
+        <v>6931998</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4462,12 +4462,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120496220</v>
+        <v>120499755</v>
       </c>
       <c r="B43" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,37 +4898,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>375471</v>
+        <v>375089</v>
       </c>
       <c r="R43" t="n">
-        <v>6932021</v>
+        <v>6931993</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120499755</v>
+        <v>120499955</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,21 +5000,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,13 +5024,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>375089</v>
+        <v>375141</v>
       </c>
       <c r="R44" t="n">
-        <v>6931993</v>
+        <v>6932029</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5074,22 +5074,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120499955</v>
+        <v>120501346</v>
       </c>
       <c r="B45" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5102,34 +5102,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>375141</v>
+        <v>375242</v>
       </c>
       <c r="R45" t="n">
-        <v>6932029</v>
+        <v>6932026</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120501346</v>
+        <v>120496220</v>
       </c>
       <c r="B46" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5204,37 +5204,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>375242</v>
+        <v>375471</v>
       </c>
       <c r="R46" t="n">
-        <v>6932026</v>
+        <v>6932021</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5278,12 +5278,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120497238</v>
+        <v>120496716</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,34 +6127,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>375407</v>
+        <v>375441</v>
       </c>
       <c r="R55" t="n">
-        <v>6931915</v>
+        <v>6931979</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6213,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120496716</v>
+        <v>120497238</v>
       </c>
       <c r="B56" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6229,34 +6229,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>375441</v>
+        <v>375407</v>
       </c>
       <c r="R56" t="n">
-        <v>6931979</v>
+        <v>6931915</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6417,10 +6417,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120498059</v>
+        <v>120497577</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6433,37 +6433,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>375156</v>
+        <v>375348</v>
       </c>
       <c r="R58" t="n">
-        <v>6931842</v>
+        <v>6931893</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6507,22 +6507,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120497577</v>
+        <v>120498059</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>375348</v>
+        <v>375156</v>
       </c>
       <c r="R59" t="n">
-        <v>6931893</v>
+        <v>6931842</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6609,12 +6609,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -9803,10 +9803,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120497095</v>
+        <v>120498296</v>
       </c>
       <c r="B91" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9815,20 +9815,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -9836,25 +9836,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>375431</v>
+        <v>375127</v>
       </c>
       <c r="R91" t="n">
-        <v>6931939</v>
+        <v>6931891</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9910,10 +9914,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120496655</v>
+        <v>120500170</v>
       </c>
       <c r="B92" t="n">
-        <v>78542</v>
+        <v>74659</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9926,37 +9930,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>375442</v>
+        <v>375161</v>
       </c>
       <c r="R92" t="n">
-        <v>6931967</v>
+        <v>6932012</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10000,12 +10004,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10119,10 +10123,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120498198</v>
+        <v>120497095</v>
       </c>
       <c r="B94" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10135,37 +10139,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>375127</v>
+        <v>375431</v>
       </c>
       <c r="R94" t="n">
-        <v>6931891</v>
+        <v>6931939</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10221,10 +10230,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120498296</v>
+        <v>120496655</v>
       </c>
       <c r="B95" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10233,50 +10242,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>375127</v>
+        <v>375442</v>
       </c>
       <c r="R95" t="n">
-        <v>6931891</v>
+        <v>6931967</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10320,22 +10320,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120500170</v>
+        <v>120501041</v>
       </c>
       <c r="B96" t="n">
-        <v>74659</v>
+        <v>57320</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10348,21 +10348,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10372,13 +10372,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>375161</v>
+        <v>375303</v>
       </c>
       <c r="R96" t="n">
-        <v>6932012</v>
+        <v>6931972</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10422,22 +10422,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120501041</v>
+        <v>120498198</v>
       </c>
       <c r="B97" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10450,37 +10450,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>375303</v>
+        <v>375127</v>
       </c>
       <c r="R97" t="n">
-        <v>6931972</v>
+        <v>6931891</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10524,19 +10524,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120496587</v>
+        <v>120497438</v>
       </c>
       <c r="B98" t="n">
         <v>78542</v>
@@ -10572,14 +10572,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>375467</v>
+        <v>375358</v>
       </c>
       <c r="R98" t="n">
-        <v>6931987</v>
+        <v>6931913</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -10638,10 +10638,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120496961</v>
+        <v>120497859</v>
       </c>
       <c r="B99" t="n">
-        <v>86895</v>
+        <v>74654</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10654,34 +10654,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>375434</v>
+        <v>375199</v>
       </c>
       <c r="R99" t="n">
-        <v>6931967</v>
+        <v>6931855</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10842,7 +10842,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120497438</v>
+        <v>120496587</v>
       </c>
       <c r="B101" t="n">
         <v>78542</v>
@@ -10878,14 +10878,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>375358</v>
+        <v>375467</v>
       </c>
       <c r="R101" t="n">
-        <v>6931913</v>
+        <v>6931987</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -10944,10 +10944,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120497859</v>
+        <v>120496961</v>
       </c>
       <c r="B102" t="n">
-        <v>74654</v>
+        <v>86895</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10960,34 +10960,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>375199</v>
+        <v>375434</v>
       </c>
       <c r="R102" t="n">
-        <v>6931855</v>
+        <v>6931967</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120498135</v>
+        <v>120500270</v>
       </c>
       <c r="B104" t="n">
         <v>74654</v>
@@ -11184,14 +11184,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>375146</v>
+        <v>375184</v>
       </c>
       <c r="R104" t="n">
-        <v>6931855</v>
+        <v>6931959</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11250,7 +11250,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120500270</v>
+        <v>120500572</v>
       </c>
       <c r="B105" t="n">
         <v>74654</v>
@@ -11286,14 +11286,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>375184</v>
+        <v>375246</v>
       </c>
       <c r="R105" t="n">
-        <v>6931959</v>
+        <v>6931915</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120500572</v>
+        <v>120498135</v>
       </c>
       <c r="B106" t="n">
         <v>74654</v>
@@ -11392,10 +11392,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>375246</v>
+        <v>375146</v>
       </c>
       <c r="R106" t="n">
-        <v>6931915</v>
+        <v>6931855</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,10 +11454,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120496992</v>
+        <v>120496167</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11466,25 +11466,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11494,10 +11494,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>375434</v>
+        <v>375480</v>
       </c>
       <c r="R107" t="n">
-        <v>6931967</v>
+        <v>6932048</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11556,10 +11556,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120498034</v>
+        <v>120496992</v>
       </c>
       <c r="B108" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11572,37 +11572,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>375273</v>
+        <v>375434</v>
       </c>
       <c r="R108" t="n">
-        <v>6931791</v>
+        <v>6931967</v>
       </c>
       <c r="S108" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11646,22 +11646,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120496167</v>
+        <v>120498034</v>
       </c>
       <c r="B109" t="n">
-        <v>79659</v>
+        <v>90598</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11670,41 +11670,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>375480</v>
+        <v>375273</v>
       </c>
       <c r="R109" t="n">
-        <v>6932048</v>
+        <v>6931791</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11748,12 +11748,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12173,7 +12173,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120497674</v>
+        <v>120499847</v>
       </c>
       <c r="B114" t="n">
         <v>78542</v>
@@ -12213,13 +12213,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>375358</v>
+        <v>375110</v>
       </c>
       <c r="R114" t="n">
-        <v>6931851</v>
+        <v>6932009</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12263,12 +12263,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12479,7 +12479,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120499847</v>
+        <v>120497674</v>
       </c>
       <c r="B117" t="n">
         <v>78542</v>
@@ -12519,13 +12519,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>375110</v>
+        <v>375358</v>
       </c>
       <c r="R117" t="n">
-        <v>6932009</v>
+        <v>6931851</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12569,12 +12569,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>

--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120497475</v>
+        <v>120500426</v>
       </c>
       <c r="B2" t="n">
-        <v>74654</v>
+        <v>91277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375335</v>
+        <v>375202</v>
       </c>
       <c r="R2" t="n">
-        <v>6931910</v>
+        <v>6931882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120501268</v>
+        <v>120501195</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>91272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375375</v>
+        <v>375322</v>
       </c>
       <c r="R3" t="n">
-        <v>6932029</v>
+        <v>6931997</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120500066</v>
+        <v>120500572</v>
       </c>
       <c r="B4" t="n">
         <v>74654</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375087</v>
+        <v>375246</v>
       </c>
       <c r="R4" t="n">
-        <v>6931962</v>
+        <v>6931915</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120501068</v>
+        <v>120501395</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375303</v>
+        <v>375202</v>
       </c>
       <c r="R5" t="n">
-        <v>6931972</v>
+        <v>6932035</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120496283</v>
+        <v>120500646</v>
       </c>
       <c r="B6" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375501</v>
+        <v>375218</v>
       </c>
       <c r="R6" t="n">
-        <v>6932016</v>
+        <v>6931932</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120497872</v>
+        <v>120496167</v>
       </c>
       <c r="B7" t="n">
-        <v>79652</v>
+        <v>79659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375194</v>
+        <v>375480</v>
       </c>
       <c r="R7" t="n">
-        <v>6931842</v>
+        <v>6932048</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120497320</v>
+        <v>120499279</v>
       </c>
       <c r="B8" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375377</v>
+        <v>375082</v>
       </c>
       <c r="R8" t="n">
-        <v>6931941</v>
+        <v>6931943</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120500398</v>
+        <v>120497560</v>
       </c>
       <c r="B9" t="n">
         <v>74654</v>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375204</v>
+        <v>375348</v>
       </c>
       <c r="R9" t="n">
-        <v>6931892</v>
+        <v>6931893</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120500301</v>
+        <v>120497095</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,37 +1507,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>375199</v>
+        <v>375431</v>
       </c>
       <c r="R10" t="n">
         <v>6931939</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120496201</v>
+        <v>120497181</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375466</v>
+        <v>375425</v>
       </c>
       <c r="R11" t="n">
-        <v>6932033</v>
+        <v>6931932</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120497639</v>
+        <v>120497512</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,42 +1716,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375295</v>
+        <v>375314</v>
       </c>
       <c r="R12" t="n">
-        <v>6931844</v>
+        <v>6931902</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120500426</v>
+        <v>120498135</v>
       </c>
       <c r="B13" t="n">
-        <v>91277</v>
+        <v>74654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,38 +1814,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375202</v>
+        <v>375146</v>
       </c>
       <c r="R13" t="n">
-        <v>6931882</v>
+        <v>6931855</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120496200</v>
+        <v>120497894</v>
       </c>
       <c r="B14" t="n">
-        <v>57431</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,41 +1916,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375489</v>
+        <v>375209</v>
       </c>
       <c r="R14" t="n">
-        <v>6932031</v>
+        <v>6931861</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120496889</v>
+        <v>120498198</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>82321</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,42 +2022,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375442</v>
+        <v>375127</v>
       </c>
       <c r="R15" t="n">
-        <v>6931967</v>
+        <v>6931891</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120497361</v>
+        <v>120497785</v>
       </c>
       <c r="B16" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,37 +2124,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>375373</v>
+        <v>375226</v>
       </c>
       <c r="R16" t="n">
-        <v>6931911</v>
+        <v>6931862</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120500669</v>
+        <v>120497675</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,34 +2231,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>375227</v>
+        <v>375261</v>
       </c>
       <c r="R17" t="n">
-        <v>6931946</v>
+        <v>6931837</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120501460</v>
+        <v>120497521</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2353,17 +2353,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375193</v>
+        <v>375302</v>
       </c>
       <c r="R18" t="n">
-        <v>6932050</v>
+        <v>6931884</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2407,22 +2407,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120501521</v>
+        <v>120499955</v>
       </c>
       <c r="B19" t="n">
-        <v>91277</v>
+        <v>74654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,38 +2431,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375185</v>
+        <v>375141</v>
       </c>
       <c r="R19" t="n">
-        <v>6932076</v>
+        <v>6932029</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120501264</v>
+        <v>120496889</v>
       </c>
       <c r="B20" t="n">
-        <v>74654</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,37 +2537,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375284</v>
+        <v>375442</v>
       </c>
       <c r="R20" t="n">
-        <v>6932030</v>
+        <v>6931967</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2611,22 +2616,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120497233</v>
+        <v>120498265</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,37 +2644,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375377</v>
+        <v>375189</v>
       </c>
       <c r="R21" t="n">
-        <v>6931941</v>
+        <v>6931835</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2725,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120497894</v>
+        <v>120497639</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,37 +2751,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375209</v>
+        <v>375295</v>
       </c>
       <c r="R22" t="n">
-        <v>6931861</v>
+        <v>6931844</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2827,7 +2842,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120497371</v>
+        <v>120500669</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2863,14 +2878,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375373</v>
+        <v>375227</v>
       </c>
       <c r="R23" t="n">
-        <v>6931911</v>
+        <v>6931946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120497689</v>
+        <v>120500798</v>
       </c>
       <c r="B24" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,37 +2960,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375261</v>
+        <v>375272</v>
       </c>
       <c r="R24" t="n">
-        <v>6931837</v>
+        <v>6931942</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3019,22 +3034,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120499317</v>
+        <v>120500737</v>
       </c>
       <c r="B25" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3062,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375056</v>
+        <v>375228</v>
       </c>
       <c r="R25" t="n">
-        <v>6931933</v>
+        <v>6931976</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3148,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120499806</v>
+        <v>120500508</v>
       </c>
       <c r="B26" t="n">
         <v>74654</v>
@@ -3169,14 +3184,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375096</v>
+        <v>375241</v>
       </c>
       <c r="R26" t="n">
-        <v>6932009</v>
+        <v>6931842</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120496270</v>
+        <v>120497366</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,42 +3266,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375458</v>
+        <v>375373</v>
       </c>
       <c r="R27" t="n">
-        <v>6932005</v>
+        <v>6931911</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3330,22 +3340,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120500971</v>
+        <v>120500455</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3358,34 +3368,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375284</v>
+        <v>375202</v>
       </c>
       <c r="R28" t="n">
-        <v>6931977</v>
+        <v>6931882</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120500133</v>
+        <v>120500170</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>74659</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3484,13 +3494,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375087</v>
+        <v>375161</v>
       </c>
       <c r="R29" t="n">
-        <v>6931962</v>
+        <v>6932012</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3534,22 +3544,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120498167</v>
+        <v>120500270</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3562,21 +3572,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3586,13 +3596,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375259</v>
+        <v>375184</v>
       </c>
       <c r="R30" t="n">
-        <v>6931809</v>
+        <v>6931959</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3636,22 +3646,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120500431</v>
+        <v>120500398</v>
       </c>
       <c r="B31" t="n">
-        <v>5189</v>
+        <v>74654</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3660,43 +3670,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>375202</v>
+        <v>375204</v>
       </c>
       <c r="R31" t="n">
-        <v>6931882</v>
+        <v>6931892</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,7 +3760,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120500548</v>
+        <v>120501264</v>
       </c>
       <c r="B32" t="n">
         <v>74654</v>
@@ -3795,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375251</v>
+        <v>375284</v>
       </c>
       <c r="R32" t="n">
-        <v>6931887</v>
+        <v>6932030</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120500737</v>
+        <v>120501041</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3878,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,13 +3902,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>375228</v>
+        <v>375303</v>
       </c>
       <c r="R33" t="n">
-        <v>6931976</v>
+        <v>6931972</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3947,22 +3952,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120496215</v>
+        <v>120500431</v>
       </c>
       <c r="B34" t="n">
-        <v>74654</v>
+        <v>5189</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,38 +3976,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>375488</v>
+        <v>375202</v>
       </c>
       <c r="R34" t="n">
-        <v>6932012</v>
+        <v>6931882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120499540</v>
+        <v>120499206</v>
       </c>
       <c r="B35" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,37 +4087,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>375059</v>
+        <v>375100</v>
       </c>
       <c r="R35" t="n">
-        <v>6931932</v>
+        <v>6931935</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4151,22 +4161,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120497004</v>
+        <v>120497577</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,42 +4189,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>375434</v>
+        <v>375348</v>
       </c>
       <c r="R36" t="n">
-        <v>6931967</v>
+        <v>6931893</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4258,22 +4263,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120500798</v>
+        <v>120496215</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,37 +4291,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>375272</v>
+        <v>375488</v>
       </c>
       <c r="R37" t="n">
-        <v>6931942</v>
+        <v>6932012</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4360,22 +4365,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120501129</v>
+        <v>120499847</v>
       </c>
       <c r="B38" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,34 +4393,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>375306</v>
+        <v>375110</v>
       </c>
       <c r="R38" t="n">
-        <v>6931998</v>
+        <v>6932009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4479,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120500508</v>
+        <v>120500624</v>
       </c>
       <c r="B39" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4490,37 +4495,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>375241</v>
+        <v>375268</v>
       </c>
       <c r="R39" t="n">
-        <v>6931842</v>
+        <v>6931899</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4564,22 +4569,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120501470</v>
+        <v>120500688</v>
       </c>
       <c r="B40" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4592,21 +4597,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,13 +4621,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>375193</v>
+        <v>375271</v>
       </c>
       <c r="R40" t="n">
-        <v>6932050</v>
+        <v>6931912</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4678,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120497106</v>
+        <v>120500467</v>
       </c>
       <c r="B41" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4694,37 +4699,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>375431</v>
+        <v>375202</v>
       </c>
       <c r="R41" t="n">
-        <v>6931939</v>
+        <v>6931882</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4780,10 +4785,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120496987</v>
+        <v>120496270</v>
       </c>
       <c r="B42" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4796,37 +4801,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>375434</v>
+        <v>375458</v>
       </c>
       <c r="R42" t="n">
-        <v>6931967</v>
+        <v>6932005</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4870,22 +4880,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120499755</v>
+        <v>120500232</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>74640</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4894,25 +4904,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,13 +4932,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>375089</v>
+        <v>375177</v>
       </c>
       <c r="R43" t="n">
-        <v>6931993</v>
+        <v>6931992</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4972,22 +4982,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120499955</v>
+        <v>120496201</v>
       </c>
       <c r="B44" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,37 +5010,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>375141</v>
+        <v>375466</v>
       </c>
       <c r="R44" t="n">
-        <v>6932029</v>
+        <v>6932033</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5074,19 +5084,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120501346</v>
+        <v>120496987</v>
       </c>
       <c r="B45" t="n">
         <v>82321</v>
@@ -5122,14 +5132,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>375242</v>
+        <v>375434</v>
       </c>
       <c r="R45" t="n">
-        <v>6932026</v>
+        <v>6931967</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120496220</v>
+        <v>120501346</v>
       </c>
       <c r="B46" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5204,37 +5214,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>375471</v>
+        <v>375242</v>
       </c>
       <c r="R46" t="n">
-        <v>6932021</v>
+        <v>6932026</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5278,22 +5288,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120498265</v>
+        <v>120501129</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5306,42 +5316,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>375189</v>
+        <v>375306</v>
       </c>
       <c r="R47" t="n">
-        <v>6931835</v>
+        <v>6931998</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5385,22 +5390,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120497181</v>
+        <v>120501079</v>
       </c>
       <c r="B48" t="n">
-        <v>90576</v>
+        <v>74654</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5413,34 +5418,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>375425</v>
+        <v>375303</v>
       </c>
       <c r="R48" t="n">
-        <v>6931932</v>
+        <v>6931972</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5499,10 +5504,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120496981</v>
+        <v>120499181</v>
       </c>
       <c r="B49" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5515,34 +5520,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>375434</v>
+        <v>375122</v>
       </c>
       <c r="R49" t="n">
-        <v>6931967</v>
+        <v>6931924</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,10 +5606,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120497512</v>
+        <v>120496168</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5613,38 +5618,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>375314</v>
+        <v>375480</v>
       </c>
       <c r="R50" t="n">
-        <v>6931902</v>
+        <v>6932048</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5703,7 +5708,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120497560</v>
+        <v>120498087</v>
       </c>
       <c r="B51" t="n">
         <v>74654</v>
@@ -5739,17 +5744,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>375348</v>
+        <v>375142</v>
       </c>
       <c r="R51" t="n">
-        <v>6931893</v>
+        <v>6931841</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5793,22 +5798,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120499056</v>
+        <v>120498159</v>
       </c>
       <c r="B52" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5821,37 +5826,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>375113</v>
+        <v>375259</v>
       </c>
       <c r="R52" t="n">
-        <v>6931901</v>
+        <v>6931809</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5895,22 +5905,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120500474</v>
+        <v>120500569</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5923,37 +5933,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>375192</v>
+        <v>375255</v>
       </c>
       <c r="R53" t="n">
-        <v>6931870</v>
+        <v>6931846</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6009,10 +6024,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120500232</v>
+        <v>120499300</v>
       </c>
       <c r="B54" t="n">
-        <v>74640</v>
+        <v>90576</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6021,25 +6036,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>306</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6049,10 +6064,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>375177</v>
+        <v>375082</v>
       </c>
       <c r="R54" t="n">
-        <v>6931992</v>
+        <v>6931943</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6111,10 +6126,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120496716</v>
+        <v>120496220</v>
       </c>
       <c r="B55" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6127,21 +6142,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6151,13 +6166,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>375441</v>
+        <v>375471</v>
       </c>
       <c r="R55" t="n">
-        <v>6931979</v>
+        <v>6932021</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6201,19 +6216,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120497238</v>
+        <v>120497674</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6249,17 +6264,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>375407</v>
+        <v>375358</v>
       </c>
       <c r="R56" t="n">
-        <v>6931915</v>
+        <v>6931851</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6303,22 +6318,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120497366</v>
+        <v>120499755</v>
       </c>
       <c r="B57" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6331,37 +6346,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>375373</v>
+        <v>375089</v>
       </c>
       <c r="R57" t="n">
-        <v>6931911</v>
+        <v>6931993</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6405,22 +6420,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120497577</v>
+        <v>120497004</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6433,37 +6448,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>375348</v>
+        <v>375434</v>
       </c>
       <c r="R58" t="n">
-        <v>6931893</v>
+        <v>6931967</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6507,22 +6527,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120498059</v>
+        <v>120501470</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6535,37 +6555,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>375156</v>
+        <v>375193</v>
       </c>
       <c r="R59" t="n">
-        <v>6931842</v>
+        <v>6932050</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6609,22 +6629,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120499206</v>
+        <v>120501266</v>
       </c>
       <c r="B60" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6637,21 +6657,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6681,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>375100</v>
+        <v>375284</v>
       </c>
       <c r="R60" t="n">
-        <v>6931935</v>
+        <v>6932030</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,7 +6743,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120499181</v>
+        <v>120500301</v>
       </c>
       <c r="B61" t="n">
         <v>74654</v>
@@ -6759,14 +6779,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>375122</v>
+        <v>375199</v>
       </c>
       <c r="R61" t="n">
-        <v>6931924</v>
+        <v>6931939</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6825,10 +6845,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120500292</v>
+        <v>120501080</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>77883</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6837,46 +6857,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>375184</v>
+        <v>375315</v>
       </c>
       <c r="R62" t="n">
-        <v>6931949</v>
+        <v>6932001</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6920,22 +6935,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120501205</v>
+        <v>120500971</v>
       </c>
       <c r="B63" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6948,21 +6963,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6972,10 +6987,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>375324</v>
+        <v>375284</v>
       </c>
       <c r="R63" t="n">
-        <v>6932016</v>
+        <v>6931977</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7034,10 +7049,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120496943</v>
+        <v>120497182</v>
       </c>
       <c r="B64" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7050,42 +7065,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>375442</v>
+        <v>375418</v>
       </c>
       <c r="R64" t="n">
-        <v>6931967</v>
+        <v>6931935</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7129,22 +7139,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120500646</v>
+        <v>120498167</v>
       </c>
       <c r="B65" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7157,21 +7167,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7181,13 +7191,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>375218</v>
+        <v>375259</v>
       </c>
       <c r="R65" t="n">
-        <v>6931932</v>
+        <v>6931809</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7231,22 +7241,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120498159</v>
+        <v>120497438</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7259,39 +7269,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>375259</v>
+        <v>375358</v>
       </c>
       <c r="R66" t="n">
-        <v>6931809</v>
+        <v>6931913</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7350,10 +7355,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120498154</v>
+        <v>120496200</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7362,41 +7367,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>375133</v>
+        <v>375489</v>
       </c>
       <c r="R67" t="n">
-        <v>6931873</v>
+        <v>6932031</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7452,10 +7457,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120498087</v>
+        <v>120500459</v>
       </c>
       <c r="B68" t="n">
-        <v>74654</v>
+        <v>90576</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7468,34 +7473,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>375142</v>
+        <v>375202</v>
       </c>
       <c r="R68" t="n">
-        <v>6931841</v>
+        <v>6931882</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7554,10 +7559,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120499279</v>
+        <v>120501296</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7570,34 +7575,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>375082</v>
+        <v>375253</v>
       </c>
       <c r="R69" t="n">
-        <v>6931943</v>
+        <v>6932049</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7656,10 +7661,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120501296</v>
+        <v>120501217</v>
       </c>
       <c r="B70" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7672,34 +7677,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>375253</v>
+        <v>375303</v>
       </c>
       <c r="R70" t="n">
-        <v>6932049</v>
+        <v>6932020</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7758,10 +7763,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120501266</v>
+        <v>120501205</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7774,21 +7779,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7798,10 +7803,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>375284</v>
+        <v>375324</v>
       </c>
       <c r="R71" t="n">
-        <v>6932030</v>
+        <v>6932016</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7860,10 +7865,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120501195</v>
+        <v>120498059</v>
       </c>
       <c r="B72" t="n">
-        <v>91272</v>
+        <v>90580</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7872,41 +7877,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>375322</v>
+        <v>375156</v>
       </c>
       <c r="R72" t="n">
-        <v>6931997</v>
+        <v>6931842</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7950,22 +7955,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120501079</v>
+        <v>120499997</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>90576</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7978,21 +7983,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8002,13 +8007,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>375303</v>
+        <v>375124</v>
       </c>
       <c r="R73" t="n">
-        <v>6931972</v>
+        <v>6932043</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8052,22 +8057,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120500569</v>
+        <v>120499317</v>
       </c>
       <c r="B74" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8080,42 +8085,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>375255</v>
+        <v>375056</v>
       </c>
       <c r="R74" t="n">
-        <v>6931846</v>
+        <v>6931933</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8159,19 +8159,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120496230</v>
+        <v>120496992</v>
       </c>
       <c r="B75" t="n">
         <v>78542</v>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>375458</v>
+        <v>375434</v>
       </c>
       <c r="R75" t="n">
-        <v>6932005</v>
+        <v>6931967</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8261,22 +8261,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120497610</v>
+        <v>120500133</v>
       </c>
       <c r="B76" t="n">
-        <v>74640</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8285,41 +8285,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>375299</v>
+        <v>375087</v>
       </c>
       <c r="R76" t="n">
-        <v>6931859</v>
+        <v>6931962</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8363,22 +8363,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120499552</v>
+        <v>120497610</v>
       </c>
       <c r="B77" t="n">
-        <v>78542</v>
+        <v>74640</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8387,38 +8387,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>375086</v>
+        <v>375299</v>
       </c>
       <c r="R77" t="n">
-        <v>6931968</v>
+        <v>6931859</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,10 +8477,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120499351</v>
+        <v>120496587</v>
       </c>
       <c r="B78" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8493,37 +8493,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>375034</v>
+        <v>375467</v>
       </c>
       <c r="R78" t="n">
-        <v>6931932</v>
+        <v>6931987</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8567,22 +8567,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120499300</v>
+        <v>120496283</v>
       </c>
       <c r="B79" t="n">
-        <v>90576</v>
+        <v>74654</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8595,34 +8595,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>375082</v>
+        <v>375501</v>
       </c>
       <c r="R79" t="n">
-        <v>6931943</v>
+        <v>6932016</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8681,10 +8681,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120500467</v>
+        <v>120499729</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8697,21 +8697,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>375202</v>
+        <v>375119</v>
       </c>
       <c r="R80" t="n">
-        <v>6931882</v>
+        <v>6931975</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120500459</v>
+        <v>120497859</v>
       </c>
       <c r="B81" t="n">
-        <v>90576</v>
+        <v>74654</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8799,34 +8799,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>375202</v>
+        <v>375199</v>
       </c>
       <c r="R81" t="n">
-        <v>6931882</v>
+        <v>6931855</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8885,10 +8885,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120500624</v>
+        <v>120499806</v>
       </c>
       <c r="B82" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>375268</v>
+        <v>375096</v>
       </c>
       <c r="R82" t="n">
-        <v>6931899</v>
+        <v>6932009</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8975,22 +8975,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120500586</v>
+        <v>120499351</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9003,34 +9003,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>375246</v>
+        <v>375034</v>
       </c>
       <c r="R83" t="n">
-        <v>6931915</v>
+        <v>6931932</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9089,10 +9089,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120501231</v>
+        <v>120496716</v>
       </c>
       <c r="B84" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9105,37 +9105,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>375356</v>
+        <v>375441</v>
       </c>
       <c r="R84" t="n">
-        <v>6932023</v>
+        <v>6931979</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9179,22 +9179,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120501217</v>
+        <v>120496943</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9207,37 +9207,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>375303</v>
+        <v>375442</v>
       </c>
       <c r="R85" t="n">
-        <v>6932020</v>
+        <v>6931967</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9281,19 +9286,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120496512</v>
+        <v>120497320</v>
       </c>
       <c r="B86" t="n">
         <v>74654</v>
@@ -9333,13 +9338,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>375467</v>
+        <v>375377</v>
       </c>
       <c r="R86" t="n">
-        <v>6931984</v>
+        <v>6931941</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9383,22 +9388,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120496168</v>
+        <v>120496961</v>
       </c>
       <c r="B87" t="n">
-        <v>79652</v>
+        <v>86895</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9407,25 +9412,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9435,10 +9440,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>375480</v>
+        <v>375434</v>
       </c>
       <c r="R87" t="n">
-        <v>6932048</v>
+        <v>6931967</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9497,10 +9502,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120497182</v>
+        <v>120498154</v>
       </c>
       <c r="B88" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9513,34 +9518,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>375418</v>
+        <v>375133</v>
       </c>
       <c r="R88" t="n">
-        <v>6931935</v>
+        <v>6931873</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9599,7 +9604,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120497432</v>
+        <v>120500066</v>
       </c>
       <c r="B89" t="n">
         <v>74654</v>
@@ -9635,17 +9640,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>375365</v>
+        <v>375087</v>
       </c>
       <c r="R89" t="n">
-        <v>6931921</v>
+        <v>6931962</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9689,19 +9694,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120497521</v>
+        <v>120501068</v>
       </c>
       <c r="B90" t="n">
         <v>78542</v>
@@ -9737,17 +9742,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>375302</v>
+        <v>375303</v>
       </c>
       <c r="R90" t="n">
-        <v>6931884</v>
+        <v>6931972</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9791,22 +9796,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120498296</v>
+        <v>120500548</v>
       </c>
       <c r="B91" t="n">
-        <v>57431</v>
+        <v>74654</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9815,47 +9820,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>375127</v>
+        <v>375251</v>
       </c>
       <c r="R91" t="n">
-        <v>6931891</v>
+        <v>6931887</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9914,10 +9910,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120500170</v>
+        <v>120500292</v>
       </c>
       <c r="B92" t="n">
-        <v>74659</v>
+        <v>57320</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9930,37 +9926,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>375161</v>
+        <v>375184</v>
       </c>
       <c r="R92" t="n">
-        <v>6932012</v>
+        <v>6931949</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10004,22 +10005,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120497785</v>
+        <v>120500474</v>
       </c>
       <c r="B93" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10032,42 +10033,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>375226</v>
+        <v>375192</v>
       </c>
       <c r="R93" t="n">
-        <v>6931862</v>
+        <v>6931870</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10111,22 +10107,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120497095</v>
+        <v>120500586</v>
       </c>
       <c r="B94" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10139,42 +10135,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>375431</v>
+        <v>375246</v>
       </c>
       <c r="R94" t="n">
-        <v>6931939</v>
+        <v>6931915</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10230,10 +10221,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120496655</v>
+        <v>120499844</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>5189</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10242,41 +10233,46 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>375442</v>
+        <v>375110</v>
       </c>
       <c r="R95" t="n">
-        <v>6931967</v>
+        <v>6932009</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10320,22 +10316,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120501041</v>
+        <v>120499540</v>
       </c>
       <c r="B96" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10348,21 +10344,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10372,13 +10368,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>375303</v>
+        <v>375059</v>
       </c>
       <c r="R96" t="n">
-        <v>6931972</v>
+        <v>6931932</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10434,10 +10430,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120498198</v>
+        <v>120497371</v>
       </c>
       <c r="B97" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10450,21 +10446,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10474,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>375127</v>
+        <v>375373</v>
       </c>
       <c r="R97" t="n">
-        <v>6931891</v>
+        <v>6931911</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10536,10 +10532,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120497438</v>
+        <v>120497361</v>
       </c>
       <c r="B98" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10552,37 +10548,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>375358</v>
+        <v>375373</v>
       </c>
       <c r="R98" t="n">
-        <v>6931913</v>
+        <v>6931911</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10626,22 +10622,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120497859</v>
+        <v>120497233</v>
       </c>
       <c r="B99" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10654,37 +10650,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>375199</v>
+        <v>375377</v>
       </c>
       <c r="R99" t="n">
-        <v>6931855</v>
+        <v>6931941</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10728,22 +10724,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120499729</v>
+        <v>120499056</v>
       </c>
       <c r="B100" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10756,34 +10752,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>375119</v>
+        <v>375113</v>
       </c>
       <c r="R100" t="n">
-        <v>6931975</v>
+        <v>6931901</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10842,10 +10838,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120496587</v>
+        <v>120501521</v>
       </c>
       <c r="B101" t="n">
-        <v>78542</v>
+        <v>91277</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10854,25 +10850,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10882,13 +10878,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>375467</v>
+        <v>375185</v>
       </c>
       <c r="R101" t="n">
-        <v>6931987</v>
+        <v>6932076</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10932,22 +10928,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120496961</v>
+        <v>120496981</v>
       </c>
       <c r="B102" t="n">
-        <v>86895</v>
+        <v>90598</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10960,21 +10956,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11046,10 +11042,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120501395</v>
+        <v>120498034</v>
       </c>
       <c r="B103" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11062,37 +11058,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>375202</v>
+        <v>375273</v>
       </c>
       <c r="R103" t="n">
-        <v>6932035</v>
+        <v>6931791</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11136,22 +11132,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120500270</v>
+        <v>120497872</v>
       </c>
       <c r="B104" t="n">
-        <v>74654</v>
+        <v>79652</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11160,38 +11156,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>375184</v>
+        <v>375194</v>
       </c>
       <c r="R104" t="n">
-        <v>6931959</v>
+        <v>6931842</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11250,10 +11246,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120500572</v>
+        <v>120497238</v>
       </c>
       <c r="B105" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11266,21 +11262,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11290,7 +11286,7 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>375246</v>
+        <v>375407</v>
       </c>
       <c r="R105" t="n">
         <v>6931915</v>
@@ -11352,7 +11348,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120498135</v>
+        <v>120497432</v>
       </c>
       <c r="B106" t="n">
         <v>74654</v>
@@ -11392,10 +11388,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>375146</v>
+        <v>375365</v>
       </c>
       <c r="R106" t="n">
-        <v>6931855</v>
+        <v>6931921</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11454,10 +11450,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120496167</v>
+        <v>120501460</v>
       </c>
       <c r="B107" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11466,41 +11462,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>375480</v>
+        <v>375193</v>
       </c>
       <c r="R107" t="n">
-        <v>6932048</v>
+        <v>6932050</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11544,22 +11540,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120496992</v>
+        <v>120496512</v>
       </c>
       <c r="B108" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11572,21 +11568,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11596,10 +11592,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>375434</v>
+        <v>375467</v>
       </c>
       <c r="R108" t="n">
-        <v>6931967</v>
+        <v>6931984</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11658,10 +11654,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120498034</v>
+        <v>120496230</v>
       </c>
       <c r="B109" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11674,37 +11670,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>375273</v>
+        <v>375458</v>
       </c>
       <c r="R109" t="n">
-        <v>6931791</v>
+        <v>6932005</v>
       </c>
       <c r="S109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11760,10 +11756,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120500455</v>
+        <v>120501268</v>
       </c>
       <c r="B110" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11776,21 +11772,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11800,13 +11796,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>375202</v>
+        <v>375375</v>
       </c>
       <c r="R110" t="n">
-        <v>6931882</v>
+        <v>6932029</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11850,22 +11846,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120499844</v>
+        <v>120500959</v>
       </c>
       <c r="B111" t="n">
-        <v>5189</v>
+        <v>79659</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11878,39 +11874,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105930</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>375110</v>
+        <v>375284</v>
       </c>
       <c r="R111" t="n">
-        <v>6932009</v>
+        <v>6931977</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11969,10 +11960,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120501080</v>
+        <v>120501231</v>
       </c>
       <c r="B112" t="n">
-        <v>77883</v>
+        <v>57320</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11981,41 +11972,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>375315</v>
+        <v>375356</v>
       </c>
       <c r="R112" t="n">
-        <v>6932001</v>
+        <v>6932023</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12059,19 +12050,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120499997</v>
+        <v>120497106</v>
       </c>
       <c r="B113" t="n">
         <v>90576</v>
@@ -12107,17 +12098,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>375124</v>
+        <v>375431</v>
       </c>
       <c r="R113" t="n">
-        <v>6932043</v>
+        <v>6931939</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12173,7 +12164,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120499847</v>
+        <v>120496655</v>
       </c>
       <c r="B114" t="n">
         <v>78542</v>
@@ -12209,17 +12200,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>375110</v>
+        <v>375442</v>
       </c>
       <c r="R114" t="n">
-        <v>6932009</v>
+        <v>6931967</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12263,22 +12254,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120500959</v>
+        <v>120497475</v>
       </c>
       <c r="B115" t="n">
-        <v>79659</v>
+        <v>74654</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12287,25 +12278,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12315,10 +12306,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>375284</v>
+        <v>375335</v>
       </c>
       <c r="R115" t="n">
-        <v>6931977</v>
+        <v>6931910</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12377,7 +12368,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120500688</v>
+        <v>120499552</v>
       </c>
       <c r="B116" t="n">
         <v>78542</v>
@@ -12417,13 +12408,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>375271</v>
+        <v>375086</v>
       </c>
       <c r="R116" t="n">
-        <v>6931912</v>
+        <v>6931968</v>
       </c>
       <c r="S116" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12467,22 +12458,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120497674</v>
+        <v>120498296</v>
       </c>
       <c r="B117" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12491,41 +12482,50 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>375358</v>
+        <v>375127</v>
       </c>
       <c r="R117" t="n">
-        <v>6931851</v>
+        <v>6931891</v>
       </c>
       <c r="S117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12569,12 +12569,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>

--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120500426</v>
+        <v>120501129</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
+        <v>74654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375202</v>
+        <v>375306</v>
       </c>
       <c r="R2" t="n">
-        <v>6931882</v>
+        <v>6931998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120501195</v>
+        <v>120497371</v>
       </c>
       <c r="B3" t="n">
-        <v>91272</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375322</v>
+        <v>375373</v>
       </c>
       <c r="R3" t="n">
-        <v>6931997</v>
+        <v>6931911</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120500572</v>
+        <v>120497095</v>
       </c>
       <c r="B4" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375246</v>
+        <v>375431</v>
       </c>
       <c r="R4" t="n">
-        <v>6931915</v>
+        <v>6931939</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120501395</v>
+        <v>120497639</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1002,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375202</v>
+        <v>375295</v>
       </c>
       <c r="R5" t="n">
-        <v>6932035</v>
+        <v>6931844</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120500646</v>
+        <v>120500737</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375218</v>
+        <v>375228</v>
       </c>
       <c r="R6" t="n">
-        <v>6931932</v>
+        <v>6931976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120496167</v>
+        <v>120500959</v>
       </c>
       <c r="B7" t="n">
         <v>79659</v>
@@ -1221,14 +1231,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375480</v>
+        <v>375284</v>
       </c>
       <c r="R7" t="n">
-        <v>6932048</v>
+        <v>6931977</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120499279</v>
+        <v>120500455</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375082</v>
+        <v>375202</v>
       </c>
       <c r="R8" t="n">
-        <v>6931943</v>
+        <v>6931882</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120497560</v>
+        <v>120500688</v>
       </c>
       <c r="B9" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375348</v>
+        <v>375271</v>
       </c>
       <c r="R9" t="n">
-        <v>6931893</v>
+        <v>6931912</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120497095</v>
+        <v>120496168</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,46 +1513,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>375431</v>
+        <v>375480</v>
       </c>
       <c r="R10" t="n">
-        <v>6931939</v>
+        <v>6932048</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120497181</v>
+        <v>120496981</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1643,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375425</v>
+        <v>375434</v>
       </c>
       <c r="R11" t="n">
-        <v>6931932</v>
+        <v>6931967</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120497512</v>
+        <v>120498135</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375314</v>
+        <v>375146</v>
       </c>
       <c r="R12" t="n">
-        <v>6931902</v>
+        <v>6931855</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120498135</v>
+        <v>120497361</v>
       </c>
       <c r="B13" t="n">
         <v>74654</v>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375146</v>
+        <v>375373</v>
       </c>
       <c r="R13" t="n">
-        <v>6931855</v>
+        <v>6931911</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120497894</v>
+        <v>120500572</v>
       </c>
       <c r="B14" t="n">
         <v>74654</v>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375209</v>
+        <v>375246</v>
       </c>
       <c r="R14" t="n">
-        <v>6931861</v>
+        <v>6931915</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120498198</v>
+        <v>120501395</v>
       </c>
       <c r="B15" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,34 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375127</v>
+        <v>375202</v>
       </c>
       <c r="R15" t="n">
-        <v>6931891</v>
+        <v>6932035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120497785</v>
+        <v>120500474</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,42 +2129,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>375226</v>
+        <v>375192</v>
       </c>
       <c r="R16" t="n">
-        <v>6931862</v>
+        <v>6931870</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,22 +2203,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120497675</v>
+        <v>120498159</v>
       </c>
       <c r="B17" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,37 +2231,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>375261</v>
+        <v>375259</v>
       </c>
       <c r="R17" t="n">
-        <v>6931837</v>
+        <v>6931809</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2305,22 +2310,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120497521</v>
+        <v>120499206</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375302</v>
+        <v>375100</v>
       </c>
       <c r="R18" t="n">
-        <v>6931884</v>
+        <v>6931935</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120499955</v>
+        <v>120497475</v>
       </c>
       <c r="B19" t="n">
         <v>74654</v>
@@ -2455,14 +2460,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375141</v>
+        <v>375335</v>
       </c>
       <c r="R19" t="n">
-        <v>6932029</v>
+        <v>6931910</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120496889</v>
+        <v>120496512</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>74654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,42 +2542,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375442</v>
+        <v>375467</v>
       </c>
       <c r="R20" t="n">
-        <v>6931967</v>
+        <v>6931984</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2616,22 +2616,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120498265</v>
+        <v>120501195</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>91272</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,43 +2640,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375189</v>
+        <v>375322</v>
       </c>
       <c r="R21" t="n">
-        <v>6931835</v>
+        <v>6931997</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120497639</v>
+        <v>120497577</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,42 +2746,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375295</v>
+        <v>375348</v>
       </c>
       <c r="R22" t="n">
-        <v>6931844</v>
+        <v>6931893</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2830,22 +2820,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120500669</v>
+        <v>120499540</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2858,21 +2848,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,13 +2872,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375227</v>
+        <v>375059</v>
       </c>
       <c r="R23" t="n">
-        <v>6931946</v>
+        <v>6931932</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2932,22 +2922,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120500798</v>
+        <v>120496201</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2960,34 +2950,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375272</v>
+        <v>375466</v>
       </c>
       <c r="R24" t="n">
-        <v>6931942</v>
+        <v>6932033</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3046,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120500737</v>
+        <v>120499755</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3086,13 +3076,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375228</v>
+        <v>375089</v>
       </c>
       <c r="R25" t="n">
-        <v>6931976</v>
+        <v>6931993</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3136,22 +3126,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120500508</v>
+        <v>120497610</v>
       </c>
       <c r="B26" t="n">
-        <v>74654</v>
+        <v>74640</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3150,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375241</v>
+        <v>375299</v>
       </c>
       <c r="R26" t="n">
-        <v>6931842</v>
+        <v>6931859</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120497366</v>
+        <v>120497004</v>
       </c>
       <c r="B27" t="n">
-        <v>82321</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,34 +3256,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375373</v>
+        <v>375434</v>
       </c>
       <c r="R27" t="n">
-        <v>6931911</v>
+        <v>6931967</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120500455</v>
+        <v>120499844</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>5189</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,38 +3359,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375202</v>
+        <v>375110</v>
       </c>
       <c r="R28" t="n">
-        <v>6931882</v>
+        <v>6932009</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120500170</v>
+        <v>120501521</v>
       </c>
       <c r="B29" t="n">
-        <v>74659</v>
+        <v>91277</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,38 +3466,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>67</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375161</v>
+        <v>375185</v>
       </c>
       <c r="R29" t="n">
-        <v>6932012</v>
+        <v>6932076</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120500270</v>
+        <v>120501470</v>
       </c>
       <c r="B30" t="n">
         <v>74654</v>
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375184</v>
+        <v>375193</v>
       </c>
       <c r="R30" t="n">
-        <v>6931959</v>
+        <v>6932050</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3646,12 +3646,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120501264</v>
+        <v>120496167</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
+        <v>79659</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,38 +3772,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375284</v>
+        <v>375480</v>
       </c>
       <c r="R32" t="n">
-        <v>6932030</v>
+        <v>6932048</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120501041</v>
+        <v>120497512</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3878,37 +3878,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>375303</v>
+        <v>375314</v>
       </c>
       <c r="R33" t="n">
-        <v>6931972</v>
+        <v>6931902</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3952,22 +3952,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120500431</v>
+        <v>120499552</v>
       </c>
       <c r="B34" t="n">
-        <v>5189</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,43 +3976,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>375202</v>
+        <v>375086</v>
       </c>
       <c r="R34" t="n">
-        <v>6931882</v>
+        <v>6931968</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4071,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120499206</v>
+        <v>120501217</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,21 +4082,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>375100</v>
+        <v>375303</v>
       </c>
       <c r="R35" t="n">
-        <v>6931935</v>
+        <v>6932020</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120497577</v>
+        <v>120500508</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,37 +4184,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>375348</v>
+        <v>375241</v>
       </c>
       <c r="R36" t="n">
-        <v>6931893</v>
+        <v>6931842</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4263,19 +4258,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120496215</v>
+        <v>120501079</v>
       </c>
       <c r="B37" t="n">
         <v>74654</v>
@@ -4311,17 +4306,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>375488</v>
+        <v>375303</v>
       </c>
       <c r="R37" t="n">
-        <v>6932012</v>
+        <v>6931972</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4365,22 +4360,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120499847</v>
+        <v>120500170</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>74659</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,21 +4388,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4417,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>375110</v>
+        <v>375161</v>
       </c>
       <c r="R38" t="n">
-        <v>6932009</v>
+        <v>6932012</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120500624</v>
+        <v>120501268</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,21 +4490,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4519,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>375268</v>
+        <v>375375</v>
       </c>
       <c r="R39" t="n">
-        <v>6931899</v>
+        <v>6932029</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -4581,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120500688</v>
+        <v>120500798</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4592,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>375271</v>
+        <v>375272</v>
       </c>
       <c r="R40" t="n">
-        <v>6931912</v>
+        <v>6931942</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -4683,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120500467</v>
+        <v>120496283</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,34 +4694,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>375202</v>
+        <v>375501</v>
       </c>
       <c r="R41" t="n">
-        <v>6931882</v>
+        <v>6932016</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120496270</v>
+        <v>120497432</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,42 +4796,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>375458</v>
+        <v>375365</v>
       </c>
       <c r="R42" t="n">
-        <v>6932005</v>
+        <v>6931921</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4880,22 +4870,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120500232</v>
+        <v>120501231</v>
       </c>
       <c r="B43" t="n">
-        <v>74640</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4904,25 +4894,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4932,13 +4922,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>375177</v>
+        <v>375356</v>
       </c>
       <c r="R43" t="n">
-        <v>6931992</v>
+        <v>6932023</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4982,19 +4972,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120496201</v>
+        <v>120500669</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5030,17 +5020,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>375466</v>
+        <v>375227</v>
       </c>
       <c r="R44" t="n">
-        <v>6932033</v>
+        <v>6931946</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5084,22 +5074,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120496987</v>
+        <v>120501205</v>
       </c>
       <c r="B45" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5112,34 +5102,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>375434</v>
+        <v>375324</v>
       </c>
       <c r="R45" t="n">
-        <v>6931967</v>
+        <v>6932016</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5198,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120501346</v>
+        <v>120496230</v>
       </c>
       <c r="B46" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5214,37 +5204,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>375242</v>
+        <v>375458</v>
       </c>
       <c r="R46" t="n">
-        <v>6932026</v>
+        <v>6932005</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5288,22 +5278,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120501129</v>
+        <v>120499729</v>
       </c>
       <c r="B47" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5316,34 +5306,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>375306</v>
+        <v>375119</v>
       </c>
       <c r="R47" t="n">
-        <v>6931998</v>
+        <v>6931975</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5402,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120501079</v>
+        <v>120500292</v>
       </c>
       <c r="B48" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5418,37 +5408,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>375303</v>
+        <v>375184</v>
       </c>
       <c r="R48" t="n">
-        <v>6931972</v>
+        <v>6931949</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5504,10 +5499,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120499181</v>
+        <v>120501080</v>
       </c>
       <c r="B49" t="n">
-        <v>74654</v>
+        <v>77883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5516,25 +5511,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5544,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>375122</v>
+        <v>375315</v>
       </c>
       <c r="R49" t="n">
-        <v>6931924</v>
+        <v>6932001</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5606,10 +5601,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120496168</v>
+        <v>120500426</v>
       </c>
       <c r="B50" t="n">
-        <v>79652</v>
+        <v>91277</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5618,38 +5613,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>67</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>375480</v>
+        <v>375202</v>
       </c>
       <c r="R50" t="n">
-        <v>6932048</v>
+        <v>6931882</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5708,10 +5703,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120498087</v>
+        <v>120497181</v>
       </c>
       <c r="B51" t="n">
-        <v>74654</v>
+        <v>90576</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5724,37 +5719,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>375142</v>
+        <v>375425</v>
       </c>
       <c r="R51" t="n">
-        <v>6931841</v>
+        <v>6931932</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5798,22 +5793,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120498159</v>
+        <v>120500431</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>5189</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5822,20 +5817,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5846,7 +5841,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5855,13 +5850,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>375259</v>
+        <v>375202</v>
       </c>
       <c r="R52" t="n">
-        <v>6931809</v>
+        <v>6931882</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5905,22 +5900,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120500569</v>
+        <v>120498296</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5929,20 +5924,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5950,25 +5945,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>375255</v>
+        <v>375127</v>
       </c>
       <c r="R53" t="n">
-        <v>6931846</v>
+        <v>6931891</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6012,22 +6011,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120499300</v>
+        <v>120497366</v>
       </c>
       <c r="B54" t="n">
-        <v>90576</v>
+        <v>82321</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6040,34 +6039,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>375082</v>
+        <v>375373</v>
       </c>
       <c r="R54" t="n">
-        <v>6931943</v>
+        <v>6931911</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6126,10 +6125,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120496220</v>
+        <v>120499847</v>
       </c>
       <c r="B55" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6142,37 +6141,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>375471</v>
+        <v>375110</v>
       </c>
       <c r="R55" t="n">
-        <v>6932021</v>
+        <v>6932009</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6216,19 +6215,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120497674</v>
+        <v>120497521</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6264,17 +6263,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>375358</v>
+        <v>375302</v>
       </c>
       <c r="R56" t="n">
-        <v>6931851</v>
+        <v>6931884</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6318,22 +6317,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120499755</v>
+        <v>120497182</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6346,37 +6345,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>375089</v>
+        <v>375418</v>
       </c>
       <c r="R57" t="n">
-        <v>6931993</v>
+        <v>6931935</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6420,22 +6419,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120497004</v>
+        <v>120500459</v>
       </c>
       <c r="B58" t="n">
-        <v>57336</v>
+        <v>90576</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6448,39 +6447,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>375434</v>
+        <v>375202</v>
       </c>
       <c r="R58" t="n">
-        <v>6931967</v>
+        <v>6931882</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6539,10 +6533,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120501470</v>
+        <v>120498059</v>
       </c>
       <c r="B59" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6555,37 +6549,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>375193</v>
+        <v>375156</v>
       </c>
       <c r="R59" t="n">
-        <v>6932050</v>
+        <v>6931842</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6629,22 +6623,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120501266</v>
+        <v>120497894</v>
       </c>
       <c r="B60" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6657,21 +6651,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6681,10 +6675,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>375284</v>
+        <v>375209</v>
       </c>
       <c r="R60" t="n">
-        <v>6932030</v>
+        <v>6931861</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6743,10 +6737,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120500301</v>
+        <v>120496655</v>
       </c>
       <c r="B61" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6759,37 +6753,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>375199</v>
+        <v>375442</v>
       </c>
       <c r="R61" t="n">
-        <v>6931939</v>
+        <v>6931967</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6833,22 +6827,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120501080</v>
+        <v>120498167</v>
       </c>
       <c r="B62" t="n">
-        <v>77883</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6857,41 +6851,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>375315</v>
+        <v>375259</v>
       </c>
       <c r="R62" t="n">
-        <v>6932001</v>
+        <v>6931809</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6935,22 +6929,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120500971</v>
+        <v>120497872</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6959,25 +6953,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6987,10 +6981,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>375284</v>
+        <v>375194</v>
       </c>
       <c r="R63" t="n">
-        <v>6931977</v>
+        <v>6931842</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7049,10 +7043,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120497182</v>
+        <v>120500066</v>
       </c>
       <c r="B64" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7065,37 +7059,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>375418</v>
+        <v>375087</v>
       </c>
       <c r="R64" t="n">
-        <v>6931935</v>
+        <v>6931962</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7139,19 +7133,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120498167</v>
+        <v>120501266</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7187,17 +7181,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>375259</v>
+        <v>375284</v>
       </c>
       <c r="R65" t="n">
-        <v>6931809</v>
+        <v>6932030</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7241,22 +7235,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120497438</v>
+        <v>120501041</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7269,21 +7263,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7293,10 +7287,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>375358</v>
+        <v>375303</v>
       </c>
       <c r="R66" t="n">
-        <v>6931913</v>
+        <v>6931972</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -7355,10 +7349,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120496200</v>
+        <v>120498325</v>
       </c>
       <c r="B67" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7367,20 +7361,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7389,19 +7383,24 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>375489</v>
+        <v>375189</v>
       </c>
       <c r="R67" t="n">
-        <v>6932031</v>
+        <v>6931835</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7445,22 +7444,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120500459</v>
+        <v>120500232</v>
       </c>
       <c r="B68" t="n">
-        <v>90576</v>
+        <v>74640</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7469,25 +7468,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7497,10 +7496,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>375202</v>
+        <v>375177</v>
       </c>
       <c r="R68" t="n">
-        <v>6931882</v>
+        <v>6931992</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7559,10 +7558,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120501296</v>
+        <v>120501068</v>
       </c>
       <c r="B69" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7575,37 +7574,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>375253</v>
+        <v>375303</v>
       </c>
       <c r="R69" t="n">
-        <v>6932049</v>
+        <v>6931972</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7649,19 +7648,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120501217</v>
+        <v>120500467</v>
       </c>
       <c r="B70" t="n">
         <v>78542</v>
@@ -7697,14 +7696,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>375303</v>
+        <v>375202</v>
       </c>
       <c r="R70" t="n">
-        <v>6932020</v>
+        <v>6931882</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7763,10 +7762,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120501205</v>
+        <v>120501296</v>
       </c>
       <c r="B71" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7779,34 +7778,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>375324</v>
+        <v>375253</v>
       </c>
       <c r="R71" t="n">
-        <v>6932016</v>
+        <v>6932049</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7865,10 +7864,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120498059</v>
+        <v>120496716</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>82321</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7881,34 +7880,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>375156</v>
+        <v>375441</v>
       </c>
       <c r="R72" t="n">
-        <v>6931842</v>
+        <v>6931979</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7967,10 +7966,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120499997</v>
+        <v>120499806</v>
       </c>
       <c r="B73" t="n">
-        <v>90576</v>
+        <v>74654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7983,21 +7982,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8007,10 +8006,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>375124</v>
+        <v>375096</v>
       </c>
       <c r="R73" t="n">
-        <v>6932043</v>
+        <v>6932009</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8069,7 +8068,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120499317</v>
+        <v>120497560</v>
       </c>
       <c r="B74" t="n">
         <v>74654</v>
@@ -8109,13 +8108,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>375056</v>
+        <v>375348</v>
       </c>
       <c r="R74" t="n">
-        <v>6931933</v>
+        <v>6931893</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8159,19 +8158,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120496992</v>
+        <v>120500586</v>
       </c>
       <c r="B75" t="n">
         <v>78542</v>
@@ -8207,14 +8206,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>375434</v>
+        <v>375246</v>
       </c>
       <c r="R75" t="n">
-        <v>6931967</v>
+        <v>6931915</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8273,10 +8272,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120500133</v>
+        <v>120499300</v>
       </c>
       <c r="B76" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8289,21 +8288,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8313,13 +8312,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>375087</v>
+        <v>375082</v>
       </c>
       <c r="R76" t="n">
-        <v>6931962</v>
+        <v>6931943</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8363,22 +8362,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120497610</v>
+        <v>120498198</v>
       </c>
       <c r="B77" t="n">
-        <v>74640</v>
+        <v>82321</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8387,25 +8386,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>306</v>
+        <v>1312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8415,10 +8414,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>375299</v>
+        <v>375127</v>
       </c>
       <c r="R77" t="n">
-        <v>6931859</v>
+        <v>6931891</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,10 +8476,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120496587</v>
+        <v>120498154</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8493,37 +8492,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>375467</v>
+        <v>375133</v>
       </c>
       <c r="R78" t="n">
-        <v>6931987</v>
+        <v>6931873</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8567,22 +8566,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120496283</v>
+        <v>120497438</v>
       </c>
       <c r="B79" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8595,37 +8594,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>375501</v>
+        <v>375358</v>
       </c>
       <c r="R79" t="n">
-        <v>6932016</v>
+        <v>6931913</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8669,22 +8668,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120499729</v>
+        <v>120499351</v>
       </c>
       <c r="B80" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8697,21 +8696,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8721,10 +8720,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>375119</v>
+        <v>375034</v>
       </c>
       <c r="R80" t="n">
-        <v>6931975</v>
+        <v>6931932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8783,7 +8782,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120497859</v>
+        <v>120499317</v>
       </c>
       <c r="B81" t="n">
         <v>74654</v>
@@ -8819,14 +8818,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>375199</v>
+        <v>375056</v>
       </c>
       <c r="R81" t="n">
-        <v>6931855</v>
+        <v>6931933</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8885,10 +8884,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120499806</v>
+        <v>120496992</v>
       </c>
       <c r="B82" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8901,34 +8900,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>375096</v>
+        <v>375434</v>
       </c>
       <c r="R82" t="n">
-        <v>6932009</v>
+        <v>6931967</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8987,10 +8986,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120499351</v>
+        <v>120498034</v>
       </c>
       <c r="B83" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9003,21 +9002,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9027,13 +9026,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>375034</v>
+        <v>375273</v>
       </c>
       <c r="R83" t="n">
-        <v>6931932</v>
+        <v>6931791</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9077,22 +9076,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120496716</v>
+        <v>120501264</v>
       </c>
       <c r="B84" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9105,34 +9104,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>375441</v>
+        <v>375284</v>
       </c>
       <c r="R84" t="n">
-        <v>6931979</v>
+        <v>6932030</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9191,10 +9190,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120496943</v>
+        <v>120500548</v>
       </c>
       <c r="B85" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9207,42 +9206,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>375442</v>
+        <v>375251</v>
       </c>
       <c r="R85" t="n">
-        <v>6931967</v>
+        <v>6931887</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9286,22 +9280,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120497320</v>
+        <v>120499997</v>
       </c>
       <c r="B86" t="n">
-        <v>74654</v>
+        <v>90576</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9314,37 +9308,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>375377</v>
+        <v>375124</v>
       </c>
       <c r="R86" t="n">
-        <v>6931941</v>
+        <v>6932043</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9388,12 +9382,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9502,10 +9496,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120498154</v>
+        <v>120496220</v>
       </c>
       <c r="B88" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9518,37 +9512,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>375133</v>
+        <v>375471</v>
       </c>
       <c r="R88" t="n">
-        <v>6931873</v>
+        <v>6932021</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9592,22 +9586,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120500066</v>
+        <v>120497233</v>
       </c>
       <c r="B89" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9620,37 +9614,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>375087</v>
+        <v>375377</v>
       </c>
       <c r="R89" t="n">
-        <v>6931962</v>
+        <v>6931941</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9706,10 +9700,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120501068</v>
+        <v>120499181</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9722,37 +9716,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>375303</v>
+        <v>375122</v>
       </c>
       <c r="R90" t="n">
-        <v>6931972</v>
+        <v>6931924</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9796,22 +9790,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120500548</v>
+        <v>120496270</v>
       </c>
       <c r="B91" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9824,37 +9818,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>375251</v>
+        <v>375458</v>
       </c>
       <c r="R91" t="n">
-        <v>6931887</v>
+        <v>6932005</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9898,19 +9897,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120500292</v>
+        <v>120497785</v>
       </c>
       <c r="B92" t="n">
         <v>57320</v>
@@ -9946,22 +9945,22 @@
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>375184</v>
+        <v>375226</v>
       </c>
       <c r="R92" t="n">
-        <v>6931949</v>
+        <v>6931862</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10005,22 +10004,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120500474</v>
+        <v>120496200</v>
       </c>
       <c r="B93" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10029,41 +10028,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>375192</v>
+        <v>375489</v>
       </c>
       <c r="R93" t="n">
-        <v>6931870</v>
+        <v>6932031</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10107,22 +10106,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120500586</v>
+        <v>120500624</v>
       </c>
       <c r="B94" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10135,37 +10134,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>375246</v>
+        <v>375268</v>
       </c>
       <c r="R94" t="n">
-        <v>6931915</v>
+        <v>6931899</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10209,22 +10208,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120499844</v>
+        <v>120501460</v>
       </c>
       <c r="B95" t="n">
-        <v>5189</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10233,46 +10232,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>375110</v>
+        <v>375193</v>
       </c>
       <c r="R95" t="n">
-        <v>6932009</v>
+        <v>6932050</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10316,22 +10310,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120499540</v>
+        <v>120497106</v>
       </c>
       <c r="B96" t="n">
-        <v>74654</v>
+        <v>90576</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10344,37 +10338,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>375059</v>
+        <v>375431</v>
       </c>
       <c r="R96" t="n">
-        <v>6931932</v>
+        <v>6931939</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10418,22 +10412,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120497371</v>
+        <v>120497859</v>
       </c>
       <c r="B97" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10446,21 +10440,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10470,10 +10464,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>375373</v>
+        <v>375199</v>
       </c>
       <c r="R97" t="n">
-        <v>6931911</v>
+        <v>6931855</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10532,7 +10526,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120497361</v>
+        <v>120496215</v>
       </c>
       <c r="B98" t="n">
         <v>74654</v>
@@ -10568,14 +10562,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>375373</v>
+        <v>375488</v>
       </c>
       <c r="R98" t="n">
-        <v>6931911</v>
+        <v>6932012</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10634,10 +10628,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120497233</v>
+        <v>120498087</v>
       </c>
       <c r="B99" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10650,37 +10644,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>375377</v>
+        <v>375142</v>
       </c>
       <c r="R99" t="n">
-        <v>6931941</v>
+        <v>6931841</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10724,19 +10718,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120499056</v>
+        <v>120500270</v>
       </c>
       <c r="B100" t="n">
         <v>74654</v>
@@ -10772,14 +10766,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>375113</v>
+        <v>375184</v>
       </c>
       <c r="R100" t="n">
-        <v>6931901</v>
+        <v>6931959</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10838,10 +10832,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120501521</v>
+        <v>120500301</v>
       </c>
       <c r="B101" t="n">
-        <v>91277</v>
+        <v>74654</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10850,38 +10844,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>375185</v>
+        <v>375199</v>
       </c>
       <c r="R101" t="n">
-        <v>6932076</v>
+        <v>6931939</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10940,10 +10934,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120496981</v>
+        <v>120497674</v>
       </c>
       <c r="B102" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10956,37 +10950,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>375434</v>
+        <v>375358</v>
       </c>
       <c r="R102" t="n">
-        <v>6931967</v>
+        <v>6931851</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11030,22 +11024,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120498034</v>
+        <v>120497689</v>
       </c>
       <c r="B103" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11058,37 +11052,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>375273</v>
+        <v>375261</v>
       </c>
       <c r="R103" t="n">
-        <v>6931791</v>
+        <v>6931837</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11132,22 +11126,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120497872</v>
+        <v>120501346</v>
       </c>
       <c r="B104" t="n">
-        <v>79652</v>
+        <v>82321</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11156,25 +11150,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11184,10 +11178,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>375194</v>
+        <v>375242</v>
       </c>
       <c r="R104" t="n">
-        <v>6931842</v>
+        <v>6932026</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11246,10 +11240,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120497238</v>
+        <v>120500646</v>
       </c>
       <c r="B105" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11262,34 +11256,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>375407</v>
+        <v>375218</v>
       </c>
       <c r="R105" t="n">
-        <v>6931915</v>
+        <v>6931932</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11348,10 +11342,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120497432</v>
+        <v>120496587</v>
       </c>
       <c r="B106" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11364,37 +11358,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>375365</v>
+        <v>375467</v>
       </c>
       <c r="R106" t="n">
-        <v>6931921</v>
+        <v>6931987</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11438,22 +11432,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120501460</v>
+        <v>120496987</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11466,37 +11460,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>375193</v>
+        <v>375434</v>
       </c>
       <c r="R107" t="n">
-        <v>6932050</v>
+        <v>6931967</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11540,19 +11534,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120496512</v>
+        <v>120499056</v>
       </c>
       <c r="B108" t="n">
         <v>74654</v>
@@ -11588,14 +11582,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>375467</v>
+        <v>375113</v>
       </c>
       <c r="R108" t="n">
-        <v>6931984</v>
+        <v>6931901</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11654,10 +11648,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120496230</v>
+        <v>120496943</v>
       </c>
       <c r="B109" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11670,37 +11664,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>375458</v>
+        <v>375442</v>
       </c>
       <c r="R109" t="n">
-        <v>6932005</v>
+        <v>6931967</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11756,10 +11755,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120501268</v>
+        <v>120500133</v>
       </c>
       <c r="B110" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11772,21 +11771,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11796,10 +11795,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>375375</v>
+        <v>375087</v>
       </c>
       <c r="R110" t="n">
-        <v>6932029</v>
+        <v>6931962</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -11858,10 +11857,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120500959</v>
+        <v>120500569</v>
       </c>
       <c r="B111" t="n">
-        <v>79659</v>
+        <v>57320</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11870,41 +11869,46 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>375284</v>
+        <v>375255</v>
       </c>
       <c r="R111" t="n">
-        <v>6931977</v>
+        <v>6931846</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11948,22 +11952,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120501231</v>
+        <v>120500971</v>
       </c>
       <c r="B112" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11976,37 +11980,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>375356</v>
+        <v>375284</v>
       </c>
       <c r="R112" t="n">
-        <v>6932023</v>
+        <v>6931977</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12050,22 +12054,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120497106</v>
+        <v>120496889</v>
       </c>
       <c r="B113" t="n">
-        <v>90576</v>
+        <v>57336</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12078,37 +12082,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>375431</v>
+        <v>375442</v>
       </c>
       <c r="R113" t="n">
-        <v>6931939</v>
+        <v>6931967</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12152,19 +12161,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120496655</v>
+        <v>120499279</v>
       </c>
       <c r="B114" t="n">
         <v>78542</v>
@@ -12200,17 +12209,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>375442</v>
+        <v>375082</v>
       </c>
       <c r="R114" t="n">
-        <v>6931967</v>
+        <v>6931943</v>
       </c>
       <c r="S114" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12254,22 +12263,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120497475</v>
+        <v>120497238</v>
       </c>
       <c r="B115" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12282,21 +12291,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12306,10 +12315,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>375335</v>
+        <v>375407</v>
       </c>
       <c r="R115" t="n">
-        <v>6931910</v>
+        <v>6931915</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12368,10 +12377,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120499552</v>
+        <v>120497320</v>
       </c>
       <c r="B116" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12384,37 +12393,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>375086</v>
+        <v>375377</v>
       </c>
       <c r="R116" t="n">
-        <v>6931968</v>
+        <v>6931941</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12458,22 +12467,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120498296</v>
+        <v>120499955</v>
       </c>
       <c r="B117" t="n">
-        <v>57431</v>
+        <v>74654</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12482,47 +12491,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>375127</v>
+        <v>375141</v>
       </c>
       <c r="R117" t="n">
-        <v>6931891</v>
+        <v>6932029</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120497639</v>
+        <v>120500455</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,42 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375295</v>
+        <v>375202</v>
       </c>
       <c r="R5" t="n">
-        <v>6931844</v>
+        <v>6931882</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120500455</v>
+        <v>120497639</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,37 +1308,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375202</v>
+        <v>375295</v>
       </c>
       <c r="R8" t="n">
-        <v>6931882</v>
+        <v>6931844</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120501195</v>
+        <v>120497577</v>
       </c>
       <c r="B21" t="n">
-        <v>91272</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375322</v>
+        <v>375348</v>
       </c>
       <c r="R21" t="n">
-        <v>6931997</v>
+        <v>6931893</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120497577</v>
+        <v>120499540</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,21 +2746,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375348</v>
+        <v>375059</v>
       </c>
       <c r="R22" t="n">
-        <v>6931893</v>
+        <v>6931932</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120499540</v>
+        <v>120496201</v>
       </c>
       <c r="B23" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,37 +2848,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375059</v>
+        <v>375466</v>
       </c>
       <c r="R23" t="n">
-        <v>6931932</v>
+        <v>6932033</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120496201</v>
+        <v>120499755</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -2970,17 +2970,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375466</v>
+        <v>375089</v>
       </c>
       <c r="R24" t="n">
-        <v>6932033</v>
+        <v>6931993</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120499755</v>
+        <v>120501195</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>91272</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,13 +3076,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375089</v>
+        <v>375322</v>
       </c>
       <c r="R25" t="n">
-        <v>6931993</v>
+        <v>6931997</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120500292</v>
+        <v>120497181</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5408,42 +5408,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>375184</v>
+        <v>375425</v>
       </c>
       <c r="R48" t="n">
-        <v>6931949</v>
+        <v>6931932</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5601,10 +5596,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120500426</v>
+        <v>120500292</v>
       </c>
       <c r="B50" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5613,41 +5608,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>375202</v>
+        <v>375184</v>
       </c>
       <c r="R50" t="n">
-        <v>6931882</v>
+        <v>6931949</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5691,22 +5691,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120497181</v>
+        <v>120500431</v>
       </c>
       <c r="B51" t="n">
-        <v>90576</v>
+        <v>5189</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5715,41 +5715,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>375425</v>
+        <v>375202</v>
       </c>
       <c r="R51" t="n">
-        <v>6931932</v>
+        <v>6931882</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5793,22 +5798,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120500431</v>
+        <v>120500426</v>
       </c>
       <c r="B52" t="n">
-        <v>5189</v>
+        <v>91277</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5817,33 +5822,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>67</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120498296</v>
+        <v>120497366</v>
       </c>
       <c r="B53" t="n">
-        <v>57431</v>
+        <v>82321</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5924,47 +5924,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>375127</v>
+        <v>375373</v>
       </c>
       <c r="R53" t="n">
-        <v>6931891</v>
+        <v>6931911</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,10 +6014,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120497366</v>
+        <v>120499847</v>
       </c>
       <c r="B54" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6039,34 +6030,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>375373</v>
+        <v>375110</v>
       </c>
       <c r="R54" t="n">
-        <v>6931911</v>
+        <v>6932009</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6125,7 +6116,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120499847</v>
+        <v>120497521</v>
       </c>
       <c r="B55" t="n">
         <v>78542</v>
@@ -6161,14 +6152,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>375110</v>
+        <v>375302</v>
       </c>
       <c r="R55" t="n">
-        <v>6932009</v>
+        <v>6931884</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6227,10 +6218,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120497521</v>
+        <v>120498296</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6239,38 +6230,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>375302</v>
+        <v>375127</v>
       </c>
       <c r="R56" t="n">
-        <v>6931884</v>
+        <v>6931891</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6329,10 +6329,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120497182</v>
+        <v>120500459</v>
       </c>
       <c r="B57" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6345,34 +6345,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>375418</v>
+        <v>375202</v>
       </c>
       <c r="R57" t="n">
-        <v>6931935</v>
+        <v>6931882</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6431,10 +6431,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120500459</v>
+        <v>120497182</v>
       </c>
       <c r="B58" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6447,34 +6447,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>375202</v>
+        <v>375418</v>
       </c>
       <c r="R58" t="n">
-        <v>6931882</v>
+        <v>6931935</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120498325</v>
+        <v>120496716</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7365,42 +7365,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>375189</v>
+        <v>375441</v>
       </c>
       <c r="R67" t="n">
-        <v>6931835</v>
+        <v>6931979</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7444,22 +7439,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120500232</v>
+        <v>120499806</v>
       </c>
       <c r="B68" t="n">
-        <v>74640</v>
+        <v>74654</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7468,25 +7463,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>306</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7496,10 +7491,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>375177</v>
+        <v>375096</v>
       </c>
       <c r="R68" t="n">
-        <v>6931992</v>
+        <v>6932009</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7558,10 +7553,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120501068</v>
+        <v>120497560</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7574,21 +7569,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7598,10 +7593,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>375303</v>
+        <v>375348</v>
       </c>
       <c r="R69" t="n">
-        <v>6931972</v>
+        <v>6931893</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -7660,10 +7655,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120500467</v>
+        <v>120498325</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7676,37 +7671,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>375202</v>
+        <v>375189</v>
       </c>
       <c r="R70" t="n">
-        <v>6931882</v>
+        <v>6931835</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7750,22 +7750,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120501296</v>
+        <v>120500232</v>
       </c>
       <c r="B71" t="n">
-        <v>79624</v>
+        <v>74640</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7774,38 +7774,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>375253</v>
+        <v>375177</v>
       </c>
       <c r="R71" t="n">
-        <v>6932049</v>
+        <v>6931992</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7864,10 +7864,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120496716</v>
+        <v>120501068</v>
       </c>
       <c r="B72" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7880,37 +7880,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>375441</v>
+        <v>375303</v>
       </c>
       <c r="R72" t="n">
-        <v>6931979</v>
+        <v>6931972</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7954,22 +7954,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120499806</v>
+        <v>120500467</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>375096</v>
+        <v>375202</v>
       </c>
       <c r="R73" t="n">
-        <v>6932009</v>
+        <v>6931882</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120497560</v>
+        <v>120501296</v>
       </c>
       <c r="B74" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8084,37 +8084,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>375348</v>
+        <v>375253</v>
       </c>
       <c r="R74" t="n">
-        <v>6931893</v>
+        <v>6932049</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8158,12 +8158,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8578,10 +8578,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120497438</v>
+        <v>120498034</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8594,21 +8594,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>375358</v>
+        <v>375273</v>
       </c>
       <c r="R79" t="n">
-        <v>6931913</v>
+        <v>6931791</v>
       </c>
       <c r="S79" t="n">
         <v>4</v>
@@ -8680,10 +8680,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120499351</v>
+        <v>120497438</v>
       </c>
       <c r="B80" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8696,21 +8696,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8720,13 +8720,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>375034</v>
+        <v>375358</v>
       </c>
       <c r="R80" t="n">
-        <v>6931932</v>
+        <v>6931913</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8770,19 +8770,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120499317</v>
+        <v>120499351</v>
       </c>
       <c r="B81" t="n">
         <v>74654</v>
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>375056</v>
+        <v>375034</v>
       </c>
       <c r="R81" t="n">
-        <v>6931933</v>
+        <v>6931932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8884,10 +8884,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120496992</v>
+        <v>120499317</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8900,34 +8900,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>375434</v>
+        <v>375056</v>
       </c>
       <c r="R82" t="n">
-        <v>6931967</v>
+        <v>6931933</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8986,10 +8986,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120498034</v>
+        <v>120496992</v>
       </c>
       <c r="B83" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9002,37 +9002,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>375273</v>
+        <v>375434</v>
       </c>
       <c r="R83" t="n">
-        <v>6931791</v>
+        <v>6931967</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9076,22 +9076,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120501264</v>
+        <v>120499997</v>
       </c>
       <c r="B84" t="n">
-        <v>74654</v>
+        <v>90576</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9104,34 +9104,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>375284</v>
+        <v>375124</v>
       </c>
       <c r="R84" t="n">
-        <v>6932030</v>
+        <v>6932043</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9190,7 +9190,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120500548</v>
+        <v>120501264</v>
       </c>
       <c r="B85" t="n">
         <v>74654</v>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>375251</v>
+        <v>375284</v>
       </c>
       <c r="R85" t="n">
-        <v>6931887</v>
+        <v>6932030</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9292,10 +9292,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120499997</v>
+        <v>120500548</v>
       </c>
       <c r="B86" t="n">
-        <v>90576</v>
+        <v>74654</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9308,34 +9308,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>375124</v>
+        <v>375251</v>
       </c>
       <c r="R86" t="n">
-        <v>6932043</v>
+        <v>6931887</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9394,10 +9394,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120496961</v>
+        <v>120496220</v>
       </c>
       <c r="B87" t="n">
-        <v>86895</v>
+        <v>74654</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9410,21 +9410,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9434,13 +9434,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>375434</v>
+        <v>375471</v>
       </c>
       <c r="R87" t="n">
-        <v>6931967</v>
+        <v>6932021</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9484,22 +9484,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120496220</v>
+        <v>120497233</v>
       </c>
       <c r="B88" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9512,21 +9512,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>375471</v>
+        <v>375377</v>
       </c>
       <c r="R88" t="n">
-        <v>6932021</v>
+        <v>6931941</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9598,10 +9598,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120497233</v>
+        <v>120499181</v>
       </c>
       <c r="B89" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9614,37 +9614,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>375377</v>
+        <v>375122</v>
       </c>
       <c r="R89" t="n">
-        <v>6931941</v>
+        <v>6931924</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9688,22 +9688,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120499181</v>
+        <v>120496961</v>
       </c>
       <c r="B90" t="n">
-        <v>74654</v>
+        <v>86895</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9716,34 +9716,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>375122</v>
+        <v>375434</v>
       </c>
       <c r="R90" t="n">
-        <v>6931924</v>
+        <v>6931967</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10118,10 +10118,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120500624</v>
+        <v>120501460</v>
       </c>
       <c r="B94" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10134,21 +10134,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10158,13 +10158,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>375268</v>
+        <v>375193</v>
       </c>
       <c r="R94" t="n">
-        <v>6931899</v>
+        <v>6932050</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10220,10 +10220,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120501460</v>
+        <v>120500624</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10236,21 +10236,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>375193</v>
+        <v>375268</v>
       </c>
       <c r="R95" t="n">
-        <v>6932050</v>
+        <v>6931899</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11240,10 +11240,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120500646</v>
+        <v>120496587</v>
       </c>
       <c r="B105" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11256,37 +11256,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>375218</v>
+        <v>375467</v>
       </c>
       <c r="R105" t="n">
-        <v>6931932</v>
+        <v>6931987</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11330,22 +11330,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120496587</v>
+        <v>120500646</v>
       </c>
       <c r="B106" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11358,37 +11358,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>375467</v>
+        <v>375218</v>
       </c>
       <c r="R106" t="n">
-        <v>6931987</v>
+        <v>6931932</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11432,22 +11432,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120496987</v>
+        <v>120500133</v>
       </c>
       <c r="B107" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11460,37 +11460,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>375434</v>
+        <v>375087</v>
       </c>
       <c r="R107" t="n">
-        <v>6931967</v>
+        <v>6931962</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11534,22 +11534,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120499056</v>
+        <v>120496987</v>
       </c>
       <c r="B108" t="n">
-        <v>74654</v>
+        <v>82321</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11562,34 +11562,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>375113</v>
+        <v>375434</v>
       </c>
       <c r="R108" t="n">
-        <v>6931901</v>
+        <v>6931967</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120500133</v>
+        <v>120500569</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11771,34 +11771,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>375087</v>
+        <v>375255</v>
       </c>
       <c r="R110" t="n">
-        <v>6931962</v>
+        <v>6931846</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -11857,10 +11862,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120500569</v>
+        <v>120499056</v>
       </c>
       <c r="B111" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11873,42 +11878,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>375255</v>
+        <v>375113</v>
       </c>
       <c r="R111" t="n">
-        <v>6931846</v>
+        <v>6931901</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11952,19 +11952,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120500971</v>
+        <v>120499279</v>
       </c>
       <c r="B112" t="n">
         <v>78542</v>
@@ -12000,14 +12000,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>375284</v>
+        <v>375082</v>
       </c>
       <c r="R112" t="n">
-        <v>6931977</v>
+        <v>6931943</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12066,10 +12066,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120496889</v>
+        <v>120497238</v>
       </c>
       <c r="B113" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12082,42 +12082,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lillhammarsvallen, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>375442</v>
+        <v>375407</v>
       </c>
       <c r="R113" t="n">
-        <v>6931967</v>
+        <v>6931915</v>
       </c>
       <c r="S113" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12161,22 +12156,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120499279</v>
+        <v>120497320</v>
       </c>
       <c r="B114" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12189,37 +12184,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>375082</v>
+        <v>375377</v>
       </c>
       <c r="R114" t="n">
-        <v>6931943</v>
+        <v>6931941</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12263,22 +12258,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120497238</v>
+        <v>120499955</v>
       </c>
       <c r="B115" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12291,34 +12286,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Dalstensknallen, Hjd</t>
+          <t>Långflon, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>375407</v>
+        <v>375141</v>
       </c>
       <c r="R115" t="n">
-        <v>6931915</v>
+        <v>6932029</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12377,10 +12372,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120497320</v>
+        <v>120496889</v>
       </c>
       <c r="B116" t="n">
-        <v>74654</v>
+        <v>57336</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12393,37 +12388,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>375377</v>
+        <v>375442</v>
       </c>
       <c r="R116" t="n">
-        <v>6931941</v>
+        <v>6931967</v>
       </c>
       <c r="S116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12479,10 +12479,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120499955</v>
+        <v>120500971</v>
       </c>
       <c r="B117" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12495,34 +12495,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Långflon, Hjd</t>
+          <t>Dalstensknallen, Hjd</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>375141</v>
+        <v>375284</v>
       </c>
       <c r="R117" t="n">
-        <v>6932029</v>
+        <v>6931977</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -12584,7 +12584,7 @@
         <v>120499412</v>
       </c>
       <c r="B118" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>

--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -11146,11 +11146,11 @@
         <v>120496889</v>
       </c>
       <c r="B104" t="n">
-        <v>57364</v>
+        <v>57494</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12477,11 +12477,11 @@
         <v>120497004</v>
       </c>
       <c r="B117" t="n">
-        <v>57364</v>
+        <v>57494</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">

--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -11146,7 +11146,7 @@
         <v>120496889</v>
       </c>
       <c r="B104" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>120497004</v>
       </c>
       <c r="B117" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>

--- a/artfynd/A 35362-2024 artfynd.xlsx
+++ b/artfynd/A 35362-2024 artfynd.xlsx
@@ -11146,7 +11146,7 @@
         <v>120496889</v>
       </c>
       <c r="B104" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>120497004</v>
       </c>
       <c r="B117" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
